--- a/Data/Rules/Great Lakes Rules Matrix.xlsx
+++ b/Data/Rules/Great Lakes Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>2338924</t>
@@ -513,10 +516,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AO8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -637,16 +640,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -759,16 +765,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -881,16 +890,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1003,16 +1015,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>33</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1125,16 +1140,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1247,16 +1265,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1369,16 +1390,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>35</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1490,6 +1514,9 @@
       </c>
       <c r="AN8">
         <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
